--- a/RSI Modular - copia/tabla_maestra_GXG.xlsx
+++ b/RSI Modular - copia/tabla_maestra_GXG.xlsx
@@ -504,28 +504,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="G2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="H2" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="I2" t="n">
-        <v>-0.47</v>
+        <v>-0.64</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.35</v>
+        <v>-3.37</v>
       </c>
       <c r="K2" t="n">
-        <v>0.15</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
         <v>-1.36</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="4">
@@ -633,7 +633,7 @@
         <v>-0.16</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5600000000000001</v>
@@ -798,7 +798,7 @@
         <v>-5.28</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.16</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="10">
@@ -830,7 +830,7 @@
         <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="I10" t="n">
         <v>-1.07</v>
@@ -859,28 +859,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.95</v>
+        <v>-1.08</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.42</v>
+        <v>-1.55</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.66</v>
+        <v>-0.4</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.21</v>
+        <v>-2.46</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.11</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="12">
@@ -1028,7 +1028,7 @@
         <v>-5.58</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.43</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="16">
@@ -1096,7 +1096,7 @@
         <v>-8.390000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-11.13</v>
+        <v>-9.16</v>
       </c>
     </row>
     <row r="18">
@@ -1137,7 +1137,7 @@
         <v>-2.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.24</v>
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -1228,28 +1228,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>52.4</v>
       </c>
       <c r="G2" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="H2" t="n">
-        <v>42.1</v>
+        <v>47.6</v>
       </c>
       <c r="I2" t="n">
-        <v>38.9</v>
+        <v>36.8</v>
       </c>
       <c r="J2" t="n">
-        <v>52.9</v>
+        <v>57.9</v>
       </c>
       <c r="K2" t="n">
-        <v>58.8</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="3">
@@ -1290,7 +1290,7 @@
         <v>40.7</v>
       </c>
       <c r="K3" t="n">
-        <v>46.2</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="4">
@@ -1354,10 +1354,10 @@
         <v>65</v>
       </c>
       <c r="E5" t="n">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="G5" t="n">
         <v>45.3</v>
@@ -1522,7 +1522,7 @@
         <v>22.2</v>
       </c>
       <c r="K9" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10">
@@ -1554,7 +1554,7 @@
         <v>52.9</v>
       </c>
       <c r="H10" t="n">
-        <v>62.5</v>
+        <v>64.7</v>
       </c>
       <c r="I10" t="n">
         <v>37.5</v>
@@ -1583,28 +1583,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="F11" t="n">
-        <v>42.9</v>
+        <v>40.7</v>
       </c>
       <c r="G11" t="n">
-        <v>42.9</v>
+        <v>40.7</v>
       </c>
       <c r="H11" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="I11" t="n">
-        <v>39.3</v>
+        <v>40.7</v>
       </c>
       <c r="J11" t="n">
-        <v>44.4</v>
+        <v>42.3</v>
       </c>
       <c r="K11" t="n">
-        <v>40.7</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="12">
@@ -1752,7 +1752,7 @@
         <v>23.8</v>
       </c>
       <c r="K15" t="n">
-        <v>30</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="16">
@@ -1820,7 +1820,7 @@
         <v>14.3</v>
       </c>
       <c r="K17" t="n">
-        <v>16.7</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="18">
@@ -1861,7 +1861,7 @@
         <v>25</v>
       </c>
       <c r="K18" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>*</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
